--- a/output/laminas_comunales/comunal_s_fonasa_a_2022_la_araucania.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2022_la_araucania.xlsx
@@ -375,196 +375,196 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Temuco</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="C2">
-        <v>242658</v>
+        <v>94.2438806303789</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="C3">
-        <v>74652</v>
+        <v>94.09205839971725</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Ercilla</t>
         </is>
       </c>
       <c r="C4">
-        <v>64677</v>
+        <v>93.78644894496873</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="C5">
-        <v>51482</v>
+        <v>93.73130075509332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Purén</t>
         </is>
       </c>
       <c r="C6">
-        <v>39886</v>
+        <v>93.49996356481819</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="C7">
-        <v>34608</v>
+        <v>93.30993186041709</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="C8">
-        <v>33121</v>
+        <v>93.29744969883379</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Lumaco</t>
         </is>
       </c>
       <c r="C9">
-        <v>31930</v>
+        <v>93.0256515916349</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Cholchol</t>
         </is>
       </c>
       <c r="C10">
-        <v>29912</v>
+        <v>92.93242853017615</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Teodoro Schmidt</t>
         </is>
       </c>
       <c r="C11">
-        <v>25801</v>
+        <v>92.88336293664891</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="C12">
-        <v>25401</v>
+        <v>92.88236387288607</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="C13">
-        <v>25296</v>
+        <v>92.76618153963999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="C14">
-        <v>24990</v>
+        <v>92.73281666878414</v>
       </c>
     </row>
     <row r="15">
@@ -579,277 +579,277 @@
         </is>
       </c>
       <c r="C15">
-        <v>24527</v>
+        <v>92.72266747315894</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C16">
-        <v>19377</v>
+        <v>92.29268292682927</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="C17">
-        <v>18917</v>
+        <v>91.90846681922197</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="C18">
-        <v>18173</v>
+        <v>91.87037733483766</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Curarrehue</t>
         </is>
       </c>
       <c r="C19">
-        <v>15688</v>
+        <v>91.8536266608582</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C20">
-        <v>14657</v>
+        <v>91.79646561381952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="C21">
-        <v>13557</v>
+        <v>91.6166562350429</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Lonquimay</t>
         </is>
       </c>
       <c r="C22">
-        <v>13158</v>
+        <v>91.05570640993993</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="C23">
-        <v>12873</v>
+        <v>90.91240626353338</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="C24">
-        <v>12831</v>
+        <v>90.54253228523301</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Melipeuco</t>
         </is>
       </c>
       <c r="C25">
-        <v>11352</v>
+        <v>90.26805757295655</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="C26">
-        <v>11066</v>
+        <v>90.13711014012355</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="C27">
-        <v>10041</v>
+        <v>90.06808551159358</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lumaco</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="C28">
-        <v>9030</v>
+        <v>88.83511756367014</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ercilla</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C29">
-        <v>8845</v>
+        <v>88.25206501465495</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C30">
-        <v>8434</v>
+        <v>87.60060576154095</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="C31">
-        <v>7299</v>
+        <v>87.53857398083483</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="C32">
-        <v>7280</v>
+        <v>86.12272420768713</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="C33">
-        <v>6836</v>
+        <v>80.00619850378669</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +905,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
